--- a/data/BasketAranjuez/basket_aranjuez.xlsx
+++ b/data/BasketAranjuez/basket_aranjuez.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,64 +548,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>35.6</v>
+        <v>46.25</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>35.4</v>
+        <v>38.4</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="S2" t="n">
-        <v>30.95</v>
+        <v>26.2</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>33.33</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         <v>24</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -767,7 +767,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -776,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -785,46 +785,46 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>17.28</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>16.65</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>30</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -843,61 +843,61 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>190.42</v>
+        <v>210.1</v>
       </c>
       <c r="H6" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="M6" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.78</v>
+        <v>34.11</v>
       </c>
       <c r="R6" t="n">
-        <v>30.15</v>
+        <v>30.67</v>
       </c>
       <c r="S6" t="n">
-        <v>20.52</v>
+        <v>21.91</v>
       </c>
       <c r="T6" t="n">
-        <v>53.2</v>
+        <v>52.46</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>11</v>
       </c>
       <c r="W6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -1059,19 +1059,19 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
         <v>6</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1107,16 +1107,16 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>46.67</v>
+        <v>35</v>
       </c>
       <c r="R9" t="n">
-        <v>55</v>
+        <v>41.25</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>16.67</v>
+        <v>12.5</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1127,69 +1127,69 @@
         <v>89</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>118.28</v>
+        <v>131.5</v>
       </c>
       <c r="H10" t="n">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="O10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="n">
-        <v>59.28</v>
+        <v>56.82</v>
       </c>
       <c r="R10" t="n">
-        <v>59.72</v>
+        <v>57.43</v>
       </c>
       <c r="S10" t="n">
-        <v>20.83</v>
+        <v>19.23</v>
       </c>
       <c r="T10" t="n">
-        <v>23.41</v>
+        <v>26.22</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1278,19 +1278,19 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -1299,43 +1299,43 @@
         <v>183.35</v>
       </c>
       <c r="H12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I12" t="n">
         <v>21</v>
       </c>
       <c r="J12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K12" t="n">
         <v>29</v>
       </c>
       <c r="L12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="M12" t="n">
         <v>50</v>
       </c>
       <c r="N12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.28</v>
+        <v>35.33</v>
       </c>
       <c r="R12" t="n">
-        <v>38.85</v>
+        <v>35.86</v>
       </c>
       <c r="S12" t="n">
-        <v>32.66</v>
+        <v>30.15</v>
       </c>
       <c r="T12" t="n">
-        <v>59.72</v>
+        <v>62.82</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>14</v>
       </c>
       <c r="W12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -1354,22 +1354,22 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>84.37</v>
+        <v>92.42</v>
       </c>
       <c r="H13" t="n">
         <v>60</v>
@@ -1384,13 +1384,13 @@
         <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M13" t="n">
         <v>22</v>
       </c>
       <c r="N13" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O13" t="n">
         <v>2</v>
@@ -1399,16 +1399,16 @@
         <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>33.65</v>
+        <v>31.06</v>
       </c>
       <c r="R13" t="n">
-        <v>23.61</v>
+        <v>21.79</v>
       </c>
       <c r="S13" t="n">
-        <v>33.54</v>
+        <v>30.96</v>
       </c>
       <c r="T13" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1419,39 +1419,39 @@
         <v>87</v>
       </c>
       <c r="W13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>157.2</v>
+        <v>175.3</v>
       </c>
       <c r="H14" t="n">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="I14" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J14" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1460,28 +1460,28 @@
         <v>5</v>
       </c>
       <c r="M14" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="N14" t="n">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P14" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="n">
-        <v>61.7</v>
+        <v>59.92</v>
       </c>
       <c r="R14" t="n">
-        <v>65.95</v>
+        <v>63.84</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>56.95</v>
+        <v>56.42</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1492,15 +1492,15 @@
         <v>16</v>
       </c>
       <c r="W14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
@@ -1509,34 +1509,34 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>37.12</v>
+        <v>44.63</v>
       </c>
       <c r="H15" t="n">
+        <v>16</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
         <v>14</v>
       </c>
-      <c r="I15" t="n">
-        <v>5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>10</v>
-      </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1545,16 +1545,16 @@
         <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>23.01</v>
+        <v>22.71</v>
       </c>
       <c r="R15" t="n">
         <v>25</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>3.33</v>
       </c>
       <c r="T15" t="n">
-        <v>5.56</v>
+        <v>5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>42</v>
       </c>
       <c r="W15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -1725,37 +1725,37 @@
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
+        <v>25</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="H18" t="n">
+        <v>27</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" t="n">
         <v>20</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>38.82</v>
-      </c>
-      <c r="H18" t="n">
-        <v>23</v>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>15</v>
       </c>
       <c r="K18" t="n">
         <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="O18" t="n">
         <v>4</v>
@@ -1764,16 +1764,16 @@
         <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>26.91</v>
+        <v>27.71</v>
       </c>
       <c r="R18" t="n">
-        <v>30.96</v>
+        <v>32.09</v>
       </c>
       <c r="S18" t="n">
-        <v>14.27</v>
+        <v>12.49</v>
       </c>
       <c r="T18" t="n">
-        <v>21.43</v>
+        <v>18.75</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
         <v>3</v>
       </c>
       <c r="W18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
@@ -1931,6 +1931,79 @@
       </c>
       <c r="W20" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="R21" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>100</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ubeda</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>4</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1991,28 +2064,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70.61538461538461</v>
+        <v>70.35714285714286</v>
       </c>
       <c r="B2" t="n">
-        <v>57.69230769230769</v>
+        <v>57.57142857142857</v>
       </c>
       <c r="C2" t="n">
-        <v>16.46153846153846</v>
+        <v>16.64285714285714</v>
       </c>
       <c r="D2" t="n">
-        <v>27.46153846153846</v>
+        <v>27.71428571428572</v>
       </c>
       <c r="E2" t="n">
-        <v>43.92307692307692</v>
+        <v>44.35714285714285</v>
       </c>
       <c r="F2" t="n">
-        <v>9.153846153846153</v>
+        <v>9.214285714285714</v>
       </c>
       <c r="G2" t="n">
-        <v>20.76923076923077</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92307692307692</v>
+        <v>31.21428571428572</v>
       </c>
     </row>
   </sheetData>
